--- a/src/DORD/ex02_DORD_glossary.xlsx
+++ b/src/DORD/ex02_DORD_glossary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,259 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Понятие</t>
+  </si>
+  <si>
+    <t>Определение</t>
+  </si>
+  <si>
+    <t>01.1</t>
+  </si>
+  <si>
+    <t>01.2</t>
+  </si>
+  <si>
+    <t>01.3</t>
+  </si>
+  <si>
+    <t>01.4</t>
+  </si>
+  <si>
+    <t>01.5</t>
+  </si>
+  <si>
+    <t>01.6</t>
+  </si>
+  <si>
+    <t>01.7</t>
+  </si>
+  <si>
+    <t>01.8</t>
+  </si>
+  <si>
+    <t>01.9</t>
+  </si>
+  <si>
+    <t>01.10</t>
+  </si>
+  <si>
+    <t>01.11</t>
+  </si>
+  <si>
+    <t>01.12</t>
+  </si>
+  <si>
+    <t>01.13</t>
+  </si>
+  <si>
+    <t>01.14</t>
+  </si>
+  <si>
+    <t>01.15</t>
+  </si>
+  <si>
+    <t>01.16</t>
+  </si>
+  <si>
+    <t>01.17</t>
+  </si>
+  <si>
+    <t>01.18</t>
+  </si>
+  <si>
+    <t>01.19</t>
+  </si>
+  <si>
+    <t>01.20</t>
+  </si>
+  <si>
+    <t>1. Онлайн-продажи</t>
+  </si>
+  <si>
+    <t>Продажа товаров или услуг через интернет. В контексте текста — резко возросший из-за локдауна канал сбыта для магазинов и ресторанов.</t>
+  </si>
+  <si>
+    <t>2. Локдаун</t>
+  </si>
+  <si>
+    <t>Меры на государственном уровне, направленные на ограничение передвижения людей и работы предприятий для предотвращения распространения инфекции. Является катализатором роста онлайн-продаж.</t>
+  </si>
+  <si>
+    <t>3. Стартап </t>
+  </si>
+  <si>
+    <t>Недавно созданная компания (в данном случае — силами студентов), разрабатывающая новый продукт или услугу в условиях неопределенности и пытающаяся найти масштабируемую бизнес-модель.</t>
+  </si>
+  <si>
+    <t>4. Курьер</t>
+  </si>
+  <si>
+    <t>Ключевой исполнитель в системе; физическое лицо, которое с помощью мобильного приложения получает задание, забирает заказ в точке отправления и доставляет его конечному клиенту.</t>
+  </si>
+  <si>
+    <t>5. Онлайн-система / Платформа </t>
+  </si>
+  <si>
+    <t>Центральное программное обеспечение, куда стекается вся информация о заказах и где происходит их распределение между курьерами. Ядро всего стартапа.</t>
+  </si>
+  <si>
+    <t>6. Заказ</t>
+  </si>
+  <si>
+    <t>Единица работы в системе. Содержит всю информацию о товаре, точках адреса, сроках и статусе выполнения.</t>
+  </si>
+  <si>
+    <t>7. Место комплектации (Точка A) </t>
+  </si>
+  <si>
+    <t>Место, где курьер должен забрать готовый к отправке заказ (например, склад магазина, кухня ресторана).</t>
+  </si>
+  <si>
+    <t>8. Место доставки (Точка B)</t>
+  </si>
+  <si>
+    <t>Адрес конечного клиента, куда необходимо доставить заказ.</t>
+  </si>
+  <si>
+    <t>9. Желаемый срок доставки</t>
+  </si>
+  <si>
+    <t>Ориентировочное или точное время, к которому клиент хочет получить свой заказ.</t>
+  </si>
+  <si>
+    <t>10. Оператор </t>
+  </si>
+  <si>
+    <t>сотрудник, который вручную получает заказы из разных источников (телефон, email, мессенджеры) и вносит их в онлайн-систему в едином формате.</t>
+  </si>
+  <si>
+    <t>11. Единый формат</t>
+  </si>
+  <si>
+    <t>Стандартизированная структура данных о заказе (набор полей: откуда, куда, что, когда), которая обеспечивает одинаковое понимание информации всеми участниками системы.</t>
+  </si>
+  <si>
+    <t>12. Мобильное приложение для курьеров</t>
+  </si>
+  <si>
+    <t>Инструмент, через который курьер взаимодействует с системой: просматривает, бронирует и обновляет статусы заказов.</t>
+  </si>
+  <si>
+    <t>13. Бронирование заказа</t>
+  </si>
+  <si>
+    <t>Действие курьера в мобильном приложении, в результате которого конкретный заказ закрепляется за ним и временно disappears из списка доступных для других.</t>
+  </si>
+  <si>
+    <t>14. Свободные заказы</t>
+  </si>
+  <si>
+    <t>Заказы, которые поступили в систему, но еще не были забронированы ни одним из курьеров.</t>
+  </si>
+  <si>
+    <t>15. Диспетчер</t>
+  </si>
+  <si>
+    <t>Сотрудник в системе, который осуществляет общий контроль над процессом доставки: отслеживает перемещения курьеров, оперативно решает проблемы (например, переназначает заказ другому курьеру, если первый не справляется).</t>
+  </si>
+  <si>
+    <t>16. Переназначение заказа</t>
+  </si>
+  <si>
+    <t>Функция диспетчера, позволяющая вручную изменить курьера, закрепленного за определенным заказом.</t>
+  </si>
+  <si>
+    <t>17. Бухгалтерия / Другая ИТ-система</t>
+  </si>
+  <si>
+    <t>Внешняя по отношению к платформе доставки система, предназначенная для финансового учета. В нее передаются данные для расчетов.</t>
+  </si>
+  <si>
+    <t>18. Расчет с поставщиками</t>
+  </si>
+  <si>
+    <t>Процесс оплаты услуг доставки компаниями-партнерами (магазинами и ресторанами), чьи заказы доставлялись.</t>
+  </si>
+  <si>
+    <t>19. Расчет оплаты курьеров</t>
+  </si>
+  <si>
+    <t>Процесс начисления заработной платы курьерам на основе успешно выполненных и подтвержденных в системе доставок.</t>
+  </si>
+  <si>
+    <t>20. Личный кабинет курьера </t>
+  </si>
+  <si>
+    <t>Персональный раздел в системе (чаще в мобильном приложении), где курьер может отслеживать свою статистику, историю заказов и начисленную оплату.</t>
+  </si>
+  <si>
+    <t>21. Администратор</t>
+  </si>
+  <si>
+    <t>Роль в системе, ответственная за управление пользователями: регистрация новых курьеров, назначение им прав доступа к функционалу платформы.</t>
+  </si>
+  <si>
+    <t>22. Права доступа</t>
+  </si>
+  <si>
+    <t>Набор разрешений, определяющих, к каким функциям системы имеет доступ тот или иной пользователь (курьер, диспетчер, оператор, администратор).</t>
+  </si>
+  <si>
+    <t>01.21</t>
+  </si>
+  <si>
+    <t>01.22</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -49,11 +298,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -69,9 +336,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -109,12 +376,12 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -149,7 +416,7 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -181,7 +448,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -331,9 +598,291 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51" customWidth="1"/>
+    <col min="4" max="4" width="41.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="6"/>
+    </row>
+    <row r="3" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="6"/>
+    </row>
+    <row r="23" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="6"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>